--- a/plantilla_familias.xlsx
+++ b/plantilla_familias.xlsx
@@ -1105,7 +1105,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-CR" sz="1200" b="1"/>
-              <a:t>Posición: tolerancia y apetito</a:t>
+              <a:t>Posición: tolerancia y apetito (líneas de corte del perfil)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1381,6 +1381,68 @@
           <c:yVal>
             <c:numRef>
               <c:f>'Datos'!$C$7</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$L$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$L$2:$L$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$M$2:$M$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$N$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$N$2:$N$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$O$2:$O$3</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>

--- a/plantilla_familias.xlsx
+++ b/plantilla_familias.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cliente" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyección" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fondos de pensión" sheetId="4" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -311,12 +312,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Proyección'!$C$9:$C$138</f>
+              <f>'Proyección'!$C$10:$C$138</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Proyección'!$Q$9:$Q$138</f>
+              <f>'Proyección'!$Q$10:$Q$138</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -347,12 +348,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Proyección'!$C$9:$C$138</f>
+              <f>'Proyección'!$C$10:$C$138</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Proyección'!$R$9:$R$138</f>
+              <f>'Proyección'!$R$10:$R$138</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1691,7 +1692,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>21</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2017,13 +2018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
@@ -2042,119 +2037,308 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio</t>
+        </is>
+      </c>
+      <c r="D1" s="2">
+        <v>450</v>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Pensión mensual (US$ de hoy)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Año de la meta</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0</v>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Inflación Ingresos (referencial)</t>
+        </is>
+      </c>
+      <c r="D2" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Otros ingresos mensuales (US$ de hoy)</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Monto de la meta (US$ de hoy)</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Inflación</t>
+        </is>
+      </c>
+      <c r="D3" s="4">
+        <v>0.039</v>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Gasto en el retiro (% del gasto)</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Año del aporte extraordinario</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Inflación Pensión</t>
+        </is>
+      </c>
+      <c r="D4" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Edad de inicio de la pensión</t>
+        </is>
+      </c>
+      <c r="L4" s="9">
+        <v>65</v>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Aporte extraordinario (US$ de hoy)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>0</v>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Inflación Salud (referencial)</t>
+        </is>
+      </c>
+      <c r="D5" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>Período del primer pago de pensión</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>Año de inicio del apoyo</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Ajuste Alquileres (referencial)</t>
+        </is>
+      </c>
+      <c r="D6" s="4">
         <v>0</v>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Años de apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>Apoyo anual (US$ de hoy)</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Ingresos en ₡</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Gastos</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Proyección Base</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>Valor nominal</t>
+        </is>
+      </c>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t>Términos reales</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Flujos adicionales y control de agotamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Edad</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Nominal</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Real</t>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Salario mensual ₡</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Gasto Familiar ₡</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Gasto Familiar en $</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Total Gasto Mensual</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Portafolio Inicial</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Aportes/Retiros</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Gasto % del Portafolio</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Retorno Total</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Retorno Total $</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Resultado Neto</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Portafolio Nominal Final $ (sin incluir inflación)</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Portafolio en Términos Reales</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>Gasto no cubierto por el portafolio</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="9" t="n">
+    <row r="10">
+      <c r="B10" s="9">
         <v>0</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C10" s="9">
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D10" s="9">
         <v>0</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E10" s="10">
         <v>0</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G10" s="10">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H10" s="10">
         <v>0</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I10" s="10">
         <v>0</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K10" s="10">
         <v>0</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L10" s="10">
         <v>0</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="M10" s="4">
         <v>0</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N10" s="4">
         <v>0</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O10" s="10">
         <v>0</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="P10" s="10">
         <v>0</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q10" s="10">
         <v>0</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R10" s="10">
         <v>0</v>
+      </c>
+      <c r="S10" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plantilla: el panel del asesor completa esta hoja al exportar la proyección de cada cliente. Las columnas desde la S se agregan según los flujos que declare el cliente.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2212,4 +2396,30 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Fondos de pensión complementaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ROP, FCL y pensión voluntaria: saldo, aportes, rendimiento y traslado al portafolio. El panel del asesor completa esta hoja al exportar la proyección.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/plantilla_familias.xlsx
+++ b/plantilla_familias.xlsx
@@ -807,6 +807,142 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$5</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$5</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$6</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2B3014"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:srgbClr val="2B3014"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="2B3014"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$I$6</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$J$6</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$H$7</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
             <c:size val="12"/>
             <c:spPr>
               <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
@@ -848,22 +984,22 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Datos'!$I$5</c:f>
+              <c:f>'Datos'!$I$7</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Datos'!$J$5</c:f>
+              <c:f>'Datos'!$J$7</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Datos'!$H$7</c:f>
+              <c:f>'Datos'!$H$9</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -879,22 +1015,22 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Datos'!$I$7:$I$9</c:f>
+              <c:f>'Datos'!$I$9:$I$11</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Datos'!$J$7:$J$9</c:f>
+              <c:f>'Datos'!$J$9:$J$11</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Datos'!$H$6</c:f>
+              <c:f>'Datos'!$H$8</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -947,12 +1083,12 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Datos'!$I$6</c:f>
+              <c:f>'Datos'!$I$8</c:f>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Datos'!$J$6</c:f>
+              <c:f>'Datos'!$J$8</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
@@ -1352,6 +1488,63 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
+              <c:f>'Datos'!$A$13</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                      <a:srgbClr val="6E7356"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$B$13</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$C$13</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
               <c:f>'Datos'!$A$7</c:f>
             </c:strRef>
           </c:tx>
@@ -1387,8 +1580,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
               <c:f>'Datos'!$L$1</c:f>
@@ -1418,8 +1611,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
               <c:f>'Datos'!$N$1</c:f>
@@ -1444,6 +1637,68 @@
           <c:yVal>
             <c:numRef>
               <c:f>'Datos'!$O$2:$O$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$P$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$P$2:$P$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$Q$2:$Q$3</c:f>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos'!$R$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="918042"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos'!$R$2:$R$3</c:f>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos'!$S$2:$S$3</c:f>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
@@ -2096,7 +2351,7 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>Año del aporte extraordinario</t>
+          <t>Año del aporte o de la venta</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2374,7 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>Aporte extraordinario (US$ de hoy)</t>
+          <t>Aporte o venta (US$ de hoy)</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2394,7 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>Año de inicio del apoyo</t>
+          <t>Año de inicio del retiro para dependientes</t>
         </is>
       </c>
     </row>
@@ -2152,16 +2407,21 @@
       <c r="D6" s="4">
         <v>0</v>
       </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Aporte anual (% del ingreso)</t>
+        </is>
+      </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>Años de apoyo</t>
+          <t>Años del retiro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Apoyo anual (US$ de hoy)</t>
+          <t>Retiro anual (US$ de hoy)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2675,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>ROP, FCL y pensión voluntaria: saldo, aportes, rendimiento y traslado al portafolio. El panel del asesor completa esta hoja al exportar la proyección.</t>
+          <t>ROP, FCL y pensión voluntaria con las reglas de la Ley de Protección al Trabajador (n.º 7983): el ROP se recibe como pensión mensual al pensionarse; el FCL se traslada en cada quinquenio o al terminar la relación laboral; la pensión voluntaria, desde los 57 años. El panel del asesor completa esta hoja al exportar la proyección.</t>
         </is>
       </c>
     </row>

--- a/plantilla_familias.xlsx
+++ b/plantilla_familias.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,16 +41,101 @@
       <b val="1"/>
       <sz val="11.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+      <color rgb="FF2B3014"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9.5"/>
+      <color rgb="FF5A5E44"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="FF918042"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E2010"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9.5"/>
+      <color rgb="FF2B3014"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="FF141709"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+      <color rgb="FF6B6E55"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B3014"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF918042"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF1E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F5EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -64,11 +149,49 @@
     <border>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9DDCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF2B3014"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF918042"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DDCB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9DDCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -82,6 +205,60 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/plantilla_familias.xlsx
+++ b/plantilla_familias.xlsx
@@ -19,7 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
@@ -191,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -258,6 +259,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/plantilla_familias.xlsx
+++ b/plantilla_familias.xlsx
@@ -9,6 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cliente" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyección" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ingresos" sheetId="5" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gastos" sheetId="6" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inversiones" sheetId="7" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desinversiones" sheetId="8" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fondos de pensión" sheetId="4" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
@@ -2872,4 +2876,32 @@
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>